--- a/data/trans_bre/IP18A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,67</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 7,41</t>
+          <t>-15,42; 6,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 12,71</t>
+          <t>-10,78; 12,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 8,47</t>
+          <t>-14,6; 8,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 39,88</t>
+          <t>-14,84; 28,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 13,29</t>
+          <t>-22,39; 12,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 20,87</t>
+          <t>-14,61; 20,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 14,35</t>
+          <t>-21,75; 13,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 576,34</t>
+          <t>-17,13; 48,21</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>-5,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>-5,88%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 11,43</t>
+          <t>-12,49; 11,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 18,45</t>
+          <t>-5,34; 19,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 13,22</t>
+          <t>-8,44; 13,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 37,79</t>
+          <t>-31,94; 18,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 21,51</t>
+          <t>-18,57; 23,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 35,63</t>
+          <t>-7,9; 39,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 23,77</t>
+          <t>-12,62; 25,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,9; 178,67</t>
+          <t>-35,28; 24,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-35,72</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 10,89</t>
+          <t>-13,66; 11,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 7,69</t>
+          <t>-14,78; 7,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 19,82</t>
+          <t>-8,92; 19,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-61,46; -13,08</t>
+          <t>-31,96; 53,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 15,72</t>
+          <t>-17,41; 17,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 11,35</t>
+          <t>-18,43; 10,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 36,16</t>
+          <t>-12,72; 38,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-42,18; 124,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,72</t>
+          <t>-7,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>-9,56%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 5,5</t>
+          <t>-10,77; 5,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 3,11</t>
+          <t>-12,21; 3,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 7,45</t>
+          <t>-7,59; 7,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 33,29</t>
+          <t>-26,96; 7,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 9,11</t>
+          <t>-16,15; 9,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 5,17</t>
+          <t>-18,16; 6,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 11,71</t>
+          <t>-10,7; 12,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 181,45</t>
+          <t>-30,86; 10,77</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,61</t>
+          <t>-3,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,04%</t>
+          <t>-4,13%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 4,66</t>
+          <t>-16,53; 4,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 12,0</t>
+          <t>-7,66; 12,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 7,56</t>
+          <t>-12,06; 7,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 14,89</t>
+          <t>-24,58; 12,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 7,84</t>
+          <t>-23,66; 8,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 19,66</t>
+          <t>-10,63; 19,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 11,35</t>
+          <t>-15,78; 10,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,97; 42,28</t>
+          <t>-26,79; 16,48</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,58</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>-0,08%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 19,94</t>
+          <t>-5,9; 20,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 13,24</t>
+          <t>-14,66; 15,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 8,27</t>
+          <t>-21,71; 8,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 49,67</t>
+          <t>-31,03; 28,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 33,85</t>
+          <t>-7,67; 36,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 23,53</t>
+          <t>-21,43; 26,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 14,15</t>
+          <t>-32,33; 15,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,34; 600,42</t>
+          <t>-34,23; 43,1</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>-1,78%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 2,39</t>
+          <t>-6,81; 2,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 4,44</t>
+          <t>-4,29; 4,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,6</t>
+          <t>-5,36; 3,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 16,57</t>
+          <t>-9,91; 7,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 3,9</t>
+          <t>-10,32; 3,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 6,96</t>
+          <t>-6,36; 7,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 5,72</t>
+          <t>-8,07; 5,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 60,79</t>
+          <t>-11,88; 9,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 6,87</t>
+          <t>-15,93; 6,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 12,64</t>
+          <t>-10,21; 13,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 8,18</t>
+          <t>-14,77; 9,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 28,49</t>
+          <t>-15,86; 28,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 12,27</t>
+          <t>-24,03; 11,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 20,43</t>
+          <t>-13,68; 22,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 13,65</t>
+          <t>-21,34; 16,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 48,21</t>
+          <t>-19,02; 48,04</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 11,9</t>
+          <t>-13,48; 12,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 19,78</t>
+          <t>-5,49; 18,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 13,57</t>
+          <t>-9,94; 13,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 18,15</t>
+          <t>-33,45; 17,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 23,29</t>
+          <t>-20,39; 23,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 39,1</t>
+          <t>-8,38; 35,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 25,07</t>
+          <t>-14,94; 24,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 24,68</t>
+          <t>-38,42; 21,61</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 11,97</t>
+          <t>-13,55; 10,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 7,16</t>
+          <t>-14,45; 8,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 19,07</t>
+          <t>-7,22; 19,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 53,64</t>
+          <t>-33,84; 52,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 17,95</t>
+          <t>-17,15; 15,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 10,64</t>
+          <t>-18,36; 12,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 38,07</t>
+          <t>-10,97; 36,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,18; 124,76</t>
+          <t>-45,65; 125,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 5,63</t>
+          <t>-11,3; 4,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 3,98</t>
+          <t>-12,04; 4,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 7,46</t>
+          <t>-8,31; 7,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 7,44</t>
+          <t>-23,72; 7,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 9,54</t>
+          <t>-16,41; 7,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 6,63</t>
+          <t>-17,91; 6,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 12,22</t>
+          <t>-11,63; 11,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 10,77</t>
+          <t>-28,22; 9,65</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 4,76</t>
+          <t>-17,6; 4,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 12,14</t>
+          <t>-7,58; 11,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 7,2</t>
+          <t>-11,84; 7,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 12,51</t>
+          <t>-22,14; 11,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 8,06</t>
+          <t>-25,36; 8,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 19,46</t>
+          <t>-10,42; 17,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 10,61</t>
+          <t>-15,25; 11,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 16,48</t>
+          <t>-24,64; 15,28</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 20,39</t>
+          <t>-5,8; 19,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 15,46</t>
+          <t>-16,3; 13,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 8,41</t>
+          <t>-21,57; 9,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 28,29</t>
+          <t>-29,19; 28,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 36,21</t>
+          <t>-7,73; 34,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 26,25</t>
+          <t>-23,53; 25,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 15,78</t>
+          <t>-32,82; 17,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 43,1</t>
+          <t>-33,3; 49,07</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 2,54</t>
+          <t>-6,61; 2,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 4,7</t>
+          <t>-4,11; 4,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,34</t>
+          <t>-5,02; 3,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 7,11</t>
+          <t>-11,4; 7,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 3,96</t>
+          <t>-9,82; 3,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 7,51</t>
+          <t>-6,1; 6,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 5,27</t>
+          <t>-7,54; 5,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 9,58</t>
+          <t>-13,7; 9,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>3,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 6,17</t>
+          <t>-15,78; 7,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 13,85</t>
+          <t>-10,56; 12,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 9,45</t>
+          <t>-15,82; 8,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 28,06</t>
+          <t>-19,99; 26,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 11,11</t>
+          <t>-23,04; 13,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 22,94</t>
+          <t>-14,47; 20,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 16,14</t>
+          <t>-22,75; 14,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 48,04</t>
+          <t>-23,19; 47,29</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,03</t>
+          <t>-4,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-5,88%</t>
+          <t>-5,69%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 12,35</t>
+          <t>-14,49; 11,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 18,45</t>
+          <t>-5,45; 18,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 13,5</t>
+          <t>-9,82; 13,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 17,14</t>
+          <t>-31,87; 18,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 23,3</t>
+          <t>-21,51; 21,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 35,11</t>
+          <t>-8,58; 35,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 24,53</t>
+          <t>-14,96; 23,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 21,61</t>
+          <t>-36,26; 25,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,15</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 10,36</t>
+          <t>-12,53; 10,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 8,25</t>
+          <t>-14,91; 7,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 19,98</t>
+          <t>-8,46; 19,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 52,53</t>
+          <t>-41,54; 54,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 15,0</t>
+          <t>-16,34; 15,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 12,51</t>
+          <t>-18,81; 11,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 36,88</t>
+          <t>-12,78; 36,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 125,6</t>
+          <t>-51,16; 130,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-7,75</t>
+          <t>-10,23</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-9,56%</t>
+          <t>-12,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 4,6</t>
+          <t>-11,08; 5,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 4,16</t>
+          <t>-12,46; 3,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 7,19</t>
+          <t>-7,73; 7,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 7,46</t>
+          <t>-26,98; 6,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 7,57</t>
+          <t>-16,19; 9,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 6,58</t>
+          <t>-18,2; 5,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 11,64</t>
+          <t>-10,89; 11,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 9,65</t>
+          <t>-31,67; 8,45</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,87</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-4,13%</t>
+          <t>-4,55%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 4,89</t>
+          <t>-17,36; 4,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 11,16</t>
+          <t>-6,59; 12,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 7,89</t>
+          <t>-11,98; 7,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 11,99</t>
+          <t>-23,32; 11,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 8,18</t>
+          <t>-24,88; 7,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 17,9</t>
+          <t>-9,29; 19,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 11,75</t>
+          <t>-15,85; 11,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 15,28</t>
+          <t>-26,34; 14,43</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-0,08%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 19,95</t>
+          <t>-4,64; 19,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 13,55</t>
+          <t>-15,69; 13,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 9,25</t>
+          <t>-22,06; 8,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 28,96</t>
+          <t>-27,03; 31,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 34,72</t>
+          <t>-6,55; 33,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 25,18</t>
+          <t>-23,57; 23,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 17,46</t>
+          <t>-32,94; 14,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 49,07</t>
+          <t>-30,98; 51,21</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-2,62</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-1,78%</t>
+          <t>-3,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 2,4</t>
+          <t>-6,63; 2,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 4,08</t>
+          <t>-4,5; 4,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 3,53</t>
+          <t>-4,86; 3,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 7,15</t>
+          <t>-12,16; 6,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 3,81</t>
+          <t>-9,99; 3,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 6,46</t>
+          <t>-6,69; 6,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 5,64</t>
+          <t>-7,18; 5,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 9,38</t>
+          <t>-14,99; 7,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-4,62</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-4,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-4.615571216905956</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.822352194689547</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.088444953232761</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.769467440337004</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.07335027048837374</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.02693158467261197</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.04835285394749946</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.05109712379108904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-15,78; 7,41</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-10,56; 12,71</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-15,82; 8,47</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-19,99; 26,93</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-23,04; 13,29</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-14,47; 20,87</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-22,75; 14,35</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-23,19; 47,29</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-15.78166734350711</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-10.55815069880776</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-15.82393728160363</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-19.98691122522949</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2304088010387207</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.144670236463733</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2274882936497134</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2318920247498099</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.413007501092871</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.71171445543379</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.466143622576208</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>26.92538097703864</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1329471350155922</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2086940042248973</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1434593817668813</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.4729259616865795</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,65</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,27%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-5,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-14,49; 11,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 18,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,82; 13,22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-31,87; 18,12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-21,51; 21,51</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-8,58; 35,63</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-14,96; 23,77</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-36,26; 25,29</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.7635227365659691</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.652226503253633</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.812796965209162</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.819453205010138</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.01265237866087056</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1129685753783329</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.03004467271490599</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.05689501540576969</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,38</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,96</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-4,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28,87%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-14.49333726638705</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.448023438239683</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.815447838550174</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-31.86591491681823</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2151345717911128</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.08580406606289796</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1495676066999212</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3625886510264428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-12,53; 10,89</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-14,91; 7,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,46; 19,82</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-41,54; 54,42</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-16,34; 15,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-18,81; 11,35</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-12,78; 36,16</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-51,16; 130,88</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11.42813664941725</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>18.45313802885283</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>13.22311613254949</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>18.1235015962829</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2150602008095187</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3563175406918487</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.2376827830422959</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2529131985254784</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,56</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-4,03</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-6,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-0,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-12,61%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.6775759894653954</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.383864800417191</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.962482857209928</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>17.24787905090763</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.009425622591012681</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.04577384645001047</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.09921594485239953</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.2887133167534167</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-11,08; 5,5</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-12,46; 3,11</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,73; 7,45</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-26,98; 6,42</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-16,19; 9,11</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-18,2; 5,17</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-10,89; 11,71</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-31,67; 8,45</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-12.53096475789871</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-14.90777304146885</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.455937424770859</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-41.53979208382756</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1634075143965357</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1880665892740079</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1278103928675525</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5116057128776352</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.8934151872455</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.690317686293431</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>19.81613413322123</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>54.4203802902151</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1572142488686976</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1135293209113496</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3615961638786938</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.308780860038277</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-6,04</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,25</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,87</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-9,25%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,15%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-4,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-17,36; 4,66</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 12,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-11,98; 7,56</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-23,32; 11,5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-24,88; 7,84</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-9,29; 19,66</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-15,85; 11,35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-26,34; 14,43</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-2.561613147560926</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-4.033237622711616</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3906700359035731</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-10.23456649391988</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.03995181208323891</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.06387164691166552</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.005838512320154005</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1261256632797827</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,9</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-0,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-11,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-11.07670168024893</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-12.45604564438842</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.726016610292887</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-26.98165014671322</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1619019918280346</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1819801375054673</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1088669400367547</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3166864030197817</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 19,94</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-15,69; 13,24</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-22,06; 8,27</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-27,03; 31,25</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-6,55; 33,85</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-23,57; 23,53</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-32,94; 14,15</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-30,98; 51,21</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.501550004292956</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.11266130085646</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.453258790112247</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.424510383862835</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09109481830446819</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.05165503647001801</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1170922826358053</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.08447155451592289</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,37%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-0,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-3,3%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-6.042125616071282</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.990263676293158</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.25396486153655</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.866937381639413</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.0925445148805681</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.02955926723291868</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.0314773787199257</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.04545366176601055</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-6,63; 2,39</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,5; 4,44</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-4,86; 3,6</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-12,16; 6,06</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-9,99; 3,9</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-6,69; 6,96</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-7,18; 5,72</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-14,99; 7,95</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-17.36054980766692</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.587751316996947</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-11.97706678146877</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-23.3170349668056</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.248838339361589</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.09285827381113472</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1585342493968841</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.263435891857575</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.659395631676013</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.0017433072474</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.563771533942035</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.49798694318676</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.07844117263809339</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1966186144004243</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.1134916678391982</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1443342900342783</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>7.054079165894656</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-0.5093868547730418</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-6.9016938726835</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1.427658775232554</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.1075593110085111</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.008198798478891314</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.1128413892408926</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.01790156159178441</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-4.641939156765726</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-15.69018248753518</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-22.06164873107453</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-27.03175137839289</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.06545006967129123</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.2356941044443958</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.3294281565140521</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.3097968633601887</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>19.93562045514247</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>13.24497106823034</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>8.269601538606494</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>31.24929833252091</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.3384875846241696</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2353034700643284</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.1414542948850521</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.5121454836533701</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-2.188957069932007</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.03917216508413368</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.5999394459685559</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.621320269593863</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.03370081366282521</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.0006007313773261285</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.009210165601043745</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.03298077287322352</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-6.62874224249155</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.50365704477579</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-4.857356430443297</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-12.15593506395217</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.09991804649295889</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.0669251262312521</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.07175219541276544</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1499009680245234</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2.39287712165311</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.441998658214306</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.602471159412508</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>6.058341302306067</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.03904293711142321</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.06960421218062304</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.0572334483908622</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.07949725769428159</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
